--- a/AAII_Financials/Quarterly/UUGRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UUGRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="92">
   <si>
     <t>UUGRY</t>
   </si>
@@ -656,22 +656,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -686,103 +685,111 @@
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43373</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43190</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43008</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42825</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42643</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42460</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42277</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42094</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -819,53 +826,59 @@
       <c r="N8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="3">
         <v>1223400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1198800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1144500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1170700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1160800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1056600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1117900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1172600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1239600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1124000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1050600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1138700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1117800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1133500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>1131600</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -902,53 +915,59 @@
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
         <v>169300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>181300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>158500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>164600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>149800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>152600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>161600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>167200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>159600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>153600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>153500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>170600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>162100</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -985,53 +1004,59 @@
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1054100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1017500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>985900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1006100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1011000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>904000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>956300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1005400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1080000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>970400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>897100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>968100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>955700</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1061,8 +1086,10 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1114,15 +1141,15 @@
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T12" s="3">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V12" s="3">
         <v>1400</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1132,20 +1159,26 @@
       <c r="Y12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB12" s="3">
         <v>3000</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1227,8 +1260,14 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1265,53 +1304,59 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>4100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>3700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>19400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>13400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>59700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-2900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>15500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>17300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>22200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>33900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>6400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>11100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1348,53 +1393,59 @@
       <c r="N15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="3">
         <v>272400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>288000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>259500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>359300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>247300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>236800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>233000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>261200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>262200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>246900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>219200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>232900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>241400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>236900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1421,8 +1472,10 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1459,53 +1512,59 @@
       <c r="N17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3">
         <v>786700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>778500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>736900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>857300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>685500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>710200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>704200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>770800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>756000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>723700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>650900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>760900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>754800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>721600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>683300</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1542,53 +1601,59 @@
       <c r="N18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="3">
         <v>436700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>420300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>407600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>313400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>475200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>346500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>413700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>401800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>483700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>400300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>399700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>377700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>363000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>411900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>448400</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1618,8 +1683,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1656,53 +1723,59 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>36100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>139600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-16000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-49200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-70200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-25300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>67000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>22900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>63400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>116400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-57000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-75500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>54300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-112200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-26900</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1739,53 +1812,59 @@
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>745100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>847900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>651100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>623500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>652300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>558000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>713600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>685800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>809300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>763500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>561900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>535200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>658700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>536600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>648900</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1822,53 +1901,59 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3">
         <v>193700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>100800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>134200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>127200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>162900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>114300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>164000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>165800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>204200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>141600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>147500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>122300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>136000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>119400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1905,53 +1990,59 @@
       <c r="N23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="3">
         <v>279100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>459100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>257300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>137000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>242100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>206900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>316700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>258800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>342900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>375100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>195100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>179900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>281200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>180300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>269500</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1988,53 +2079,59 @@
       <c r="N24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="3">
         <v>562800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>76800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>50000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>202600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>45300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>30100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>57500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>44500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>63500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>69600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-54400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-114400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>57000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>37500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>55200</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2116,8 +2213,14 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2154,53 +2257,59 @@
       <c r="N26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3">
         <v>-283700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>382400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>207300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-65600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>196800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>176700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>259200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>214400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>279300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>305500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>249500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>294300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>224200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>142700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2237,53 +2346,59 @@
       <c r="N27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3">
         <v>-283700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>382400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>207300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-65600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>196800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>176700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>259200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>214400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>279300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>305500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>249500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>294300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>224200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>142700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2365,8 +2480,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2403,11 +2524,11 @@
       <c r="N29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2430,11 +2551,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2442,14 +2563,20 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2531,8 +2658,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2614,8 +2747,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2652,53 +2791,59 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-36100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-139600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>16000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>49200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>70200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>25300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-67000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-22900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-63400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-116400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>57000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>75500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-54300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>112200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2735,53 +2880,59 @@
       <c r="N33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="3">
         <v>-283700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>382400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>207300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-65600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>196800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>176700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>259200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>214400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>279300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>305500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>249500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>294300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>224200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>142700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2863,8 +3014,14 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2901,141 +3058,153 @@
       <c r="N35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3">
         <v>-283700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>382400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>207300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-65600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>196800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>176700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>259200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>214400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>279300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>305500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>249500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>294300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>224200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>142700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43373</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43190</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43008</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42825</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42643</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42460</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42277</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42094</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3065,8 +3234,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3096,130 +3267,138 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2369300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2414900</v>
+      </c>
+      <c r="F41" s="3">
         <v>1990300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2028600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2161000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2094000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1454100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1371100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1767300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1782400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>6600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>6900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>421100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>860700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>976400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1150400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>669300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>771300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>397400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>316700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>695500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>124000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>327300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>292400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>278600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>464900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>321300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>145600</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>611600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>623400</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>976000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>920300</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>1004800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>1046400</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -3262,340 +3441,370 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>536800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>547100</v>
+      </c>
+      <c r="F43" s="3">
         <v>627200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>639300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>484900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>469800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>561300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>529300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>412900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>416400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>447400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>465900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>358000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>332000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>309800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>360000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>359400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>360200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>311400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>355200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>389200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>413500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>410800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>424900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>479200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>495500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>465200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>464300</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>12200</v>
+      </c>
+      <c r="F44" s="3">
         <v>13400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>13700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>31800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>30800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>29600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>27900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>27200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>27400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>15300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>15900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>16200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>24800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>24000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>24300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>21000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>20100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>17500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>17400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>22900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>27700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>29600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>36000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>38200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>50100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>53300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>18400</v>
+      </c>
+      <c r="F45" s="3">
         <v>7500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>7700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>14700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>14300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>19200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>18100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>26900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>27100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>37800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>39400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>60000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>30200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>18900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>117500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>118700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>199600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>460600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>469000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>101300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>20500</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3">
         <v>1300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>69900</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2936200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2992700</v>
+      </c>
+      <c r="F46" s="3">
         <v>3250100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3312600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2692400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2608900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3040200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2866700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2234200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2253300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1511800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1574400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>855400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1247600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1329100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1534800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1049800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1269100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>845000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>888900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1568200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1034200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>868900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>753600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>816500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1010400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>841200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>733500</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3605,246 +3814,264 @@
       <c r="E47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3">
         <v>2100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>2000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>17400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>16400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>15700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>15800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>18800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>19600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>20400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>111800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>113900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>218800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>182400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>258300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>279500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>282900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>304700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>308100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>259500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>161300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>60400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>53200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>56400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>57000</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19918000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>20301500</v>
+      </c>
+      <c r="F48" s="3">
         <v>19253700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>19624100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>17924000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>17368000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>17937700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>16913700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>16474700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>16615200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>15649200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>16296500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>15551600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>15689100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>15482600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>14906000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>14587800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>14094400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>13064000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>13351000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>14716000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>14984600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>13743500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>12557600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>13084100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>12841800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>12794300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>12521800</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>158300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>161400</v>
+      </c>
+      <c r="F49" s="3">
         <v>130900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>133400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>136700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>132500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>155200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>146300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>157200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>158600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>156100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>162500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>176000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>223600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>237600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>225000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>239500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>243300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>237400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>258600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>269600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>272100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>247900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>221400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>211800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>205400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>190800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>157200</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3926,8 +4153,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4009,91 +4242,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>851600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>868000</v>
+      </c>
+      <c r="F52" s="3">
         <v>854900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>871400</v>
       </c>
-      <c r="F52" s="3">
-        <v>816200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>790800</v>
-      </c>
       <c r="H52" s="3">
+        <v>816000</v>
+      </c>
+      <c r="I52" s="3">
+        <v>790700</v>
+      </c>
+      <c r="J52" s="3">
         <v>809500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>763300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>795000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>801800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>896100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>933100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1275000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1678800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1442500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1684100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1738600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1627300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1021000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>939300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>875600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>903000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1292400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1419300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1357400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>1029800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>1001800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>669200</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4175,91 +4420,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23936200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>24397000</v>
+      </c>
+      <c r="F54" s="3">
         <v>23562700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>24015900</v>
       </c>
-      <c r="F54" s="3">
-        <v>21666400</v>
-      </c>
-      <c r="G54" s="3">
-        <v>20994300</v>
-      </c>
       <c r="H54" s="3">
+        <v>21666300</v>
+      </c>
+      <c r="I54" s="3">
+        <v>20994200</v>
+      </c>
+      <c r="J54" s="3">
         <v>22057100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>20798000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>19769900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>19938600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>18322800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>19080700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>17972100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>18950900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>18605800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>18568700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>17798100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>17492400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>15446900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>15720700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>17734000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>17501900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>16412300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>15113300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>15530200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>15140700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>14884500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>14138600</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4289,8 +4546,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4320,506 +4579,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>81500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>83000</v>
+      </c>
+      <c r="F57" s="3">
         <v>846600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>862900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>38600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>37400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>716800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>675900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>29600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>29800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>604300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>629300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>32700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>499400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>423400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>413800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>423800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>401800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>376200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>412900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>376000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>484000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>426600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>449800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>445700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>558200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>502000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>572500</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>217700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>221900</v>
+      </c>
+      <c r="F58" s="3">
         <v>566800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>577800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>597000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>578500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>933800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>880500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>828000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>835100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>206700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>215300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>218200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>867000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>859200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1092000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1070900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>906400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>820100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>686900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>1144900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>919300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>430700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>372400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>612000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>1102500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>761200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>120200</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>184900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>188400</v>
+      </c>
+      <c r="F59" s="3">
         <v>51200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>52200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>168900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>163600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>50400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>47500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>143200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>144400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>30400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>31600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>124100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>21400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>23600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>21800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>32100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>41200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>35800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>28300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>35900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>42300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>53800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>31200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>43400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>50600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>55600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1151600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1173800</v>
+      </c>
+      <c r="F60" s="3">
         <v>1464600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1492800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1390100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1346900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1701000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1603900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1399100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1411100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>841400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>876200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>712500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1387800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1306300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1527600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1526700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1349400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1232200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1128200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1556800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1445500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>911100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>853400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>1101100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1711400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>1318800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>786100</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14955300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>15243200</v>
+      </c>
+      <c r="F61" s="3">
         <v>14727100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>15010400</v>
       </c>
-      <c r="F61" s="3">
-        <v>13342000</v>
-      </c>
-      <c r="G61" s="3">
-        <v>12928100</v>
-      </c>
       <c r="H61" s="3">
+        <v>13341900</v>
+      </c>
+      <c r="I61" s="3">
+        <v>12928000</v>
+      </c>
+      <c r="J61" s="3">
         <v>13404600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>12639400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>11803500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>11904300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>10957500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>11410700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>10217500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>10237900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>10231200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>10355600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>9527700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>9655900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>8334500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>8714600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>9645800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>9591900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>9322700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>8639100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>8489500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>7822900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>7989400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>8108900</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>425600</v>
+      </c>
+      <c r="E62" s="3">
+        <v>433800</v>
+      </c>
+      <c r="F62" s="3">
         <v>1856600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1892300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>378400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>366700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1711800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1614100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>347800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>350800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1473700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1534600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>324400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3753800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>3091000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3062500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2989800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2701600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2236500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2258800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2507100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2504500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2451800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2332200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>2410800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>2401100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>2370700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>2269600</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4901,8 +5198,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4984,8 +5287,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5067,91 +5376,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>20976500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>21380300</v>
+      </c>
+      <c r="F66" s="3">
         <v>20884900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>21286600</v>
       </c>
-      <c r="F66" s="3">
-        <v>19082500</v>
-      </c>
-      <c r="G66" s="3">
-        <v>18490600</v>
-      </c>
       <c r="H66" s="3">
+        <v>19082400</v>
+      </c>
+      <c r="I66" s="3">
+        <v>18490400</v>
+      </c>
+      <c r="J66" s="3">
         <v>19459100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>18348200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>17173100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>17319600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>15669500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>16317600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>14868500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>15379500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>14628500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>14945700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>14044200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>13706900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>11803200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>12101500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>13709600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>13541900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>12685500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>11824600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>12001300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>11935300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>11678900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>11164700</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5181,8 +5502,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5264,8 +5587,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5347,8 +5676,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5430,8 +5765,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5513,91 +5854,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1846300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1881800</v>
+      </c>
+      <c r="F72" s="3">
         <v>1562800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1592800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1522000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1474800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1504200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1418400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1569000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1582400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1633300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1700800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2044500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2859200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3309000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>2979700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3107900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>3161800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>3044800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>3408200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>3341300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>3250500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>3065400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>2671600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>2880600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>2561100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>2555100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>2112700</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5679,8 +6032,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5762,8 +6121,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5845,91 +6210,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2959700</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3016700</v>
+      </c>
+      <c r="F76" s="3">
         <v>2677800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2729300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2583900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2503700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2598000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2449700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>2596800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>2619000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>2653300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>2763100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>3103600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3571400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3977300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>3623000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>3753900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>3785600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>3643700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>3619200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>4024400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>3960000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>3726700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>3288700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>3528800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>3205300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>3205600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>2974000</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6011,96 +6388,108 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43373</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43190</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43008</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42825</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42643</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42460</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42277</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42094</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -6137,53 +6526,59 @@
       <c r="N81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="3">
         <v>-283700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>382400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>207300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-65600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>196800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>176700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>259200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>214400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>279300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>305500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>249500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>294300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>224200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>142700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6213,91 +6608,99 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>132300</v>
+      </c>
+      <c r="F83" s="3">
         <v>150300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>141700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>132700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>133900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>119500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>124500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>122900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>119700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>104100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>113500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>125000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>272300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>288000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>259500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>359300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>247300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>236800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>233000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>261200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>262200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>246900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>219200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>232900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>241400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>236900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6379,8 +6782,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6462,8 +6871,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6545,8 +6960,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6628,8 +7049,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6711,91 +7138,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>459100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>468000</v>
+      </c>
+      <c r="F89" s="3">
         <v>461400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>470300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>287300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>278400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>317200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>299100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>230000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>232000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>232400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>242000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>239300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>617500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>604500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>510200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>565500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>451800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>461600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>534600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>551000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>582500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>529800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>516900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>411600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>482600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>444800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>485500</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6825,91 +7264,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-564200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-575100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-428500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-436700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-356900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-345800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-292200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-275500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-248000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-250100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-217700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-226700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-218000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-288500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-328600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-315400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-338900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-341100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-374500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-369100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-511600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-457800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-472100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-388000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-436700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-390500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-503400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-456700</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6991,8 +7438,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7074,91 +7527,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-278200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-283500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-710200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-723900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>116700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>113000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-782600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-737900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>44800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>45200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-489600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-509800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-223300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-377800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-280400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-429400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-364900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-379700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-383100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-366700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-535400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-467800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-566400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-462800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-474500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-408200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-489100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-439100</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7188,91 +7653,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>80500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>82000</v>
+      </c>
+      <c r="F96" s="3">
         <v>158400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>161500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>76100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>73700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>151700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>143000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>71400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>72000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>126200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>131500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>64000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-258000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-128900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-247900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-122700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-232900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-109900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-220300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-123200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-250000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-116600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-215300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-113900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-223600</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-112700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-215700</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7354,8 +7827,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7437,8 +7916,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7520,91 +8005,103 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>26600</v>
+      </c>
+      <c r="F100" s="3">
         <v>122300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>124600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-20000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-19300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>261200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>246200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>359500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>362600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>285800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>297600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-134100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-368300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-514600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>387100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-315800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>274700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>25800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-487200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>563400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-323200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>47200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-16900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-126000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>65500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>200800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-17500</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7626,38 +8123,38 @@
       <c r="I101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -7686,87 +8183,99 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>207100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>211000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-126600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-129000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>384000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>372100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-204300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-192600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>634300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>639700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>28600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>29800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-118900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-128600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-190500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>467800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-115200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>346800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>104200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-319400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>578900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-208600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>10600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>37200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-188900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>139800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>156600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>28800</v>
       </c>
     </row>
